--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83F2D26-A1EF-D249-A51E-30354E1A9BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48260B21-7625-C34B-A53D-342041894CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="234">
   <si>
     <t>Surname</t>
   </si>
@@ -75,6 +75,669 @@
   </si>
   <si>
     <t>AS_3</t>
+  </si>
+  <si>
+    <t>Baureni</t>
+  </si>
+  <si>
+    <t>H250085G</t>
+  </si>
+  <si>
+    <t>HICS</t>
+  </si>
+  <si>
+    <t>Chibondwe</t>
+  </si>
+  <si>
+    <t>H250404G</t>
+  </si>
+  <si>
+    <t>Chifamba</t>
+  </si>
+  <si>
+    <t>H250027y</t>
+  </si>
+  <si>
+    <t>chimhiti</t>
+  </si>
+  <si>
+    <t>H250028M</t>
+  </si>
+  <si>
+    <t>CHOWA</t>
+  </si>
+  <si>
+    <t>H250456M</t>
+  </si>
+  <si>
+    <t>Garikai</t>
+  </si>
+  <si>
+    <t>H250776T</t>
+  </si>
+  <si>
+    <t>Gawaza</t>
+  </si>
+  <si>
+    <t>H250212M</t>
+  </si>
+  <si>
+    <t>Gurure</t>
+  </si>
+  <si>
+    <t>H250447T</t>
+  </si>
+  <si>
+    <t>GWATIDZO</t>
+  </si>
+  <si>
+    <t>H250051T</t>
+  </si>
+  <si>
+    <t>Jiri</t>
+  </si>
+  <si>
+    <t>H250082B</t>
+  </si>
+  <si>
+    <t>Juru</t>
+  </si>
+  <si>
+    <t>H250293N</t>
+  </si>
+  <si>
+    <t>Kahanda</t>
+  </si>
+  <si>
+    <t>H250407A</t>
+  </si>
+  <si>
+    <t>KATIZE</t>
+  </si>
+  <si>
+    <t>H250772G</t>
+  </si>
+  <si>
+    <t>Katonha</t>
+  </si>
+  <si>
+    <t>H250122N</t>
+  </si>
+  <si>
+    <t>Kuki</t>
+  </si>
+  <si>
+    <t>H250634C</t>
+  </si>
+  <si>
+    <t>Madembo</t>
+  </si>
+  <si>
+    <t>H250253X</t>
+  </si>
+  <si>
+    <t>MADZIVIRE</t>
+  </si>
+  <si>
+    <t>H250482B</t>
+  </si>
+  <si>
+    <t>Magorimbo</t>
+  </si>
+  <si>
+    <t>H220726Q</t>
+  </si>
+  <si>
+    <t>Mahwte</t>
+  </si>
+  <si>
+    <t>H250740W</t>
+  </si>
+  <si>
+    <t>Makhomeya</t>
+  </si>
+  <si>
+    <t>H250333E</t>
+  </si>
+  <si>
+    <t>Makope</t>
+  </si>
+  <si>
+    <t>H250525T</t>
+  </si>
+  <si>
+    <t>Makumbomana</t>
+  </si>
+  <si>
+    <t>H250038P</t>
+  </si>
+  <si>
+    <t>Mambonei</t>
+  </si>
+  <si>
+    <t>H250791G</t>
+  </si>
+  <si>
+    <t>Maneswa</t>
+  </si>
+  <si>
+    <t>H250371Y</t>
+  </si>
+  <si>
+    <t>Manjokota</t>
+  </si>
+  <si>
+    <t>H250214J</t>
+  </si>
+  <si>
+    <t>Manyanye</t>
+  </si>
+  <si>
+    <t>H250081A</t>
+  </si>
+  <si>
+    <t>Mashoro</t>
+  </si>
+  <si>
+    <t>H250320A</t>
+  </si>
+  <si>
+    <t>Masiyachengo</t>
+  </si>
+  <si>
+    <t>H250345P</t>
+  </si>
+  <si>
+    <t>MASUKUME</t>
+  </si>
+  <si>
+    <t>H250643V</t>
+  </si>
+  <si>
+    <t>Matawu</t>
+  </si>
+  <si>
+    <t>H250631A</t>
+  </si>
+  <si>
+    <t>Maulana</t>
+  </si>
+  <si>
+    <t>H250606C</t>
+  </si>
+  <si>
+    <t>MAZIRE</t>
+  </si>
+  <si>
+    <t>H250128A</t>
+  </si>
+  <si>
+    <t>Mondiwa</t>
+  </si>
+  <si>
+    <t>H250655C</t>
+  </si>
+  <si>
+    <t>MTEMBO</t>
+  </si>
+  <si>
+    <t>H250652C</t>
+  </si>
+  <si>
+    <t>Mugabe</t>
+  </si>
+  <si>
+    <t>H250393Q</t>
+  </si>
+  <si>
+    <t>Mujuru</t>
+  </si>
+  <si>
+    <t>H250037R</t>
+  </si>
+  <si>
+    <t>H250571W</t>
+  </si>
+  <si>
+    <t>Mukusha</t>
+  </si>
+  <si>
+    <t>H250643J</t>
+  </si>
+  <si>
+    <t>Munanga</t>
+  </si>
+  <si>
+    <t>H250363V</t>
+  </si>
+  <si>
+    <t>Munyawu</t>
+  </si>
+  <si>
+    <t>H250397M</t>
+  </si>
+  <si>
+    <t>Murape</t>
+  </si>
+  <si>
+    <t>H250475V</t>
+  </si>
+  <si>
+    <t>Muungani</t>
+  </si>
+  <si>
+    <t>H250126C</t>
+  </si>
+  <si>
+    <t>Nyamadzawo</t>
+  </si>
+  <si>
+    <t>H250266A</t>
+  </si>
+  <si>
+    <t>Nyazondo</t>
+  </si>
+  <si>
+    <t>H250033T</t>
+  </si>
+  <si>
+    <t>Nyevhe</t>
+  </si>
+  <si>
+    <t>H250117C</t>
+  </si>
+  <si>
+    <t>Paweni</t>
+  </si>
+  <si>
+    <t>H250335H</t>
+  </si>
+  <si>
+    <t>Rungano</t>
+  </si>
+  <si>
+    <t>H250002N</t>
+  </si>
+  <si>
+    <t>SHANGWA</t>
+  </si>
+  <si>
+    <t>H250773G</t>
+  </si>
+  <si>
+    <t>Sigauke</t>
+  </si>
+  <si>
+    <t>H250529B</t>
+  </si>
+  <si>
+    <t>Tsaha</t>
+  </si>
+  <si>
+    <t>H250415Y</t>
+  </si>
+  <si>
+    <t>Vangana</t>
+  </si>
+  <si>
+    <t>H250006V</t>
+  </si>
+  <si>
+    <t>Vevha</t>
+  </si>
+  <si>
+    <t>H250629H</t>
+  </si>
+  <si>
+    <t>Zidenga</t>
+  </si>
+  <si>
+    <t>H250576C</t>
+  </si>
+  <si>
+    <t>Amdrea</t>
+  </si>
+  <si>
+    <t>H250512W</t>
+  </si>
+  <si>
+    <t>HISA</t>
+  </si>
+  <si>
+    <t>Bare</t>
+  </si>
+  <si>
+    <t>H250078F</t>
+  </si>
+  <si>
+    <t>Bauti</t>
+  </si>
+  <si>
+    <t>H250069Y</t>
+  </si>
+  <si>
+    <t>CHARINGENO</t>
+  </si>
+  <si>
+    <t>H250184X</t>
+  </si>
+  <si>
+    <t>Chimwamurombe</t>
+  </si>
+  <si>
+    <t>H250246H</t>
+  </si>
+  <si>
+    <t>Chinake</t>
+  </si>
+  <si>
+    <t>H250101f</t>
+  </si>
+  <si>
+    <t>Chingombe</t>
+  </si>
+  <si>
+    <t>H250427H</t>
+  </si>
+  <si>
+    <t>Chiota</t>
+  </si>
+  <si>
+    <t>H210130v</t>
+  </si>
+  <si>
+    <t>Chishowerere</t>
+  </si>
+  <si>
+    <t>H250199M</t>
+  </si>
+  <si>
+    <t>Chisveto</t>
+  </si>
+  <si>
+    <t>H250352B</t>
+  </si>
+  <si>
+    <t>Chitsa</t>
+  </si>
+  <si>
+    <t>H250395M</t>
+  </si>
+  <si>
+    <t>Chiwambutsa</t>
+  </si>
+  <si>
+    <t>H250183Z</t>
+  </si>
+  <si>
+    <t>Chiwanza</t>
+  </si>
+  <si>
+    <t>H250494R</t>
+  </si>
+  <si>
+    <t>Chiwenga</t>
+  </si>
+  <si>
+    <t>H250685R</t>
+  </si>
+  <si>
+    <t>Chonzi</t>
+  </si>
+  <si>
+    <t>H250286m</t>
+  </si>
+  <si>
+    <t>Dumbreni</t>
+  </si>
+  <si>
+    <t>H250406Z</t>
+  </si>
+  <si>
+    <t>Godzi</t>
+  </si>
+  <si>
+    <t>H250830M</t>
+  </si>
+  <si>
+    <t>H250829J</t>
+  </si>
+  <si>
+    <t>Hweru</t>
+  </si>
+  <si>
+    <t>H250588F</t>
+  </si>
+  <si>
+    <t>Jasi</t>
+  </si>
+  <si>
+    <t>H250295N</t>
+  </si>
+  <si>
+    <t>Kachisi</t>
+  </si>
+  <si>
+    <t>H250637J</t>
+  </si>
+  <si>
+    <t>Kadyamusuma</t>
+  </si>
+  <si>
+    <t>H250298W</t>
+  </si>
+  <si>
+    <t>Katiyo</t>
+  </si>
+  <si>
+    <t>H250346E</t>
+  </si>
+  <si>
+    <t>KWANISAI</t>
+  </si>
+  <si>
+    <t>H250476w</t>
+  </si>
+  <si>
+    <t>Leher</t>
+  </si>
+  <si>
+    <t>H250430P</t>
+  </si>
+  <si>
+    <t>Maburuse</t>
+  </si>
+  <si>
+    <t>H250402X</t>
+  </si>
+  <si>
+    <t>Macheka</t>
+  </si>
+  <si>
+    <t>H250813X</t>
+  </si>
+  <si>
+    <t>Makoni</t>
+  </si>
+  <si>
+    <t>H250504N</t>
+  </si>
+  <si>
+    <t>Mandeya</t>
+  </si>
+  <si>
+    <t>H250574B</t>
+  </si>
+  <si>
+    <t>Mapuranga</t>
+  </si>
+  <si>
+    <t>H250450H</t>
+  </si>
+  <si>
+    <t>Mare</t>
+  </si>
+  <si>
+    <t>H250159A</t>
+  </si>
+  <si>
+    <t>Marekwa</t>
+  </si>
+  <si>
+    <t>H250401A</t>
+  </si>
+  <si>
+    <t>Matuso</t>
+  </si>
+  <si>
+    <t>H250535z</t>
+  </si>
+  <si>
+    <t>MAVINDIDZE</t>
+  </si>
+  <si>
+    <t>H250344B</t>
+  </si>
+  <si>
+    <t>Mawire</t>
+  </si>
+  <si>
+    <t>H250531A</t>
+  </si>
+  <si>
+    <t>Mawoyo</t>
+  </si>
+  <si>
+    <t>H250520X</t>
+  </si>
+  <si>
+    <t>MBISHI</t>
+  </si>
+  <si>
+    <t>H250356E</t>
+  </si>
+  <si>
+    <t>H250270X</t>
+  </si>
+  <si>
+    <t>Mukori</t>
+  </si>
+  <si>
+    <t>H250503V</t>
+  </si>
+  <si>
+    <t>Mukwara</t>
+  </si>
+  <si>
+    <t>H240380W</t>
+  </si>
+  <si>
+    <t>Murasha</t>
+  </si>
+  <si>
+    <t>H250702v</t>
+  </si>
+  <si>
+    <t>Mushayapokuvaka</t>
+  </si>
+  <si>
+    <t>H220311Y</t>
+  </si>
+  <si>
+    <t>MUSINGADI</t>
+  </si>
+  <si>
+    <t>H250125B</t>
+  </si>
+  <si>
+    <t>Mutombo</t>
+  </si>
+  <si>
+    <t>H250638X</t>
+  </si>
+  <si>
+    <t>Mutsengi</t>
+  </si>
+  <si>
+    <t>H250381f</t>
+  </si>
+  <si>
+    <t>Muzani</t>
+  </si>
+  <si>
+    <t>H250200A</t>
+  </si>
+  <si>
+    <t>Nawu</t>
+  </si>
+  <si>
+    <t>H250564T</t>
+  </si>
+  <si>
+    <t>Ndambakuwa</t>
+  </si>
+  <si>
+    <t>H250653R</t>
+  </si>
+  <si>
+    <t>Nhende</t>
+  </si>
+  <si>
+    <t>H250595R</t>
+  </si>
+  <si>
+    <t>NYAMHURI</t>
+  </si>
+  <si>
+    <t>H250585P</t>
+  </si>
+  <si>
+    <t>Pazuwa</t>
+  </si>
+  <si>
+    <t>H250575Y</t>
+  </si>
+  <si>
+    <t>Rwodzi</t>
+  </si>
+  <si>
+    <t>H250124X</t>
+  </si>
+  <si>
+    <t>Shambare</t>
+  </si>
+  <si>
+    <t>H250039J</t>
+  </si>
+  <si>
+    <t>Sokisi</t>
+  </si>
+  <si>
+    <t>H250639J</t>
+  </si>
+  <si>
+    <t>Tamirepi</t>
+  </si>
+  <si>
+    <t>H250026e</t>
+  </si>
+  <si>
+    <t>Tsepete</t>
+  </si>
+  <si>
+    <t>H250567V</t>
+  </si>
+  <si>
+    <t>Zacharia</t>
+  </si>
+  <si>
+    <t>H250474N</t>
+  </si>
+  <si>
+    <t>ZAMBUKO</t>
+  </si>
+  <si>
+    <t>H250194E</t>
   </si>
 </sst>
 </file>
@@ -686,787 +1349,1495 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+      <c r="A2" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>15</v>
+      </c>
       <c r="D2" s="4"/>
       <c r="H2" s="5"/>
       <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
+      <c r="A3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
       <c r="D3" s="4"/>
       <c r="H3" s="5"/>
       <c r="M3" s="18"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>15</v>
+      </c>
       <c r="D4" s="4"/>
       <c r="H4" s="5"/>
       <c r="M4" s="18"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="15"/>
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>15</v>
+      </c>
       <c r="D5" s="4"/>
       <c r="H5" s="5"/>
       <c r="M5" s="18"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
       <c r="D6" s="4"/>
       <c r="H6" s="5"/>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
       <c r="D7" s="4"/>
       <c r="H7" s="5"/>
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="H8" s="5"/>
       <c r="M8" s="6"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="H9" s="5"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="H10" s="5"/>
       <c r="M10" s="6"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
+      <c r="A11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="H11" s="5"/>
       <c r="M11" s="6"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="H12" s="5"/>
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="H13" s="5"/>
       <c r="M13" s="6"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="H14" s="5"/>
       <c r="M14" s="6"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="H15" s="5"/>
       <c r="M15" s="6"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="H16" s="5"/>
       <c r="M16" s="6"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="H17" s="5"/>
       <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="H18" s="5"/>
       <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
       <c r="D19" s="4"/>
       <c r="H19" s="5"/>
       <c r="M19" s="6"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
       <c r="D20" s="4"/>
       <c r="H20" s="5"/>
       <c r="M20" s="6"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
       <c r="D21" s="4"/>
       <c r="H21" s="5"/>
       <c r="M21" s="6"/>
     </row>
     <row r="22" spans="1:13">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="H22" s="5"/>
       <c r="M22" s="6"/>
     </row>
     <row r="23" spans="1:13">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="H23" s="5"/>
       <c r="M23" s="6"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="H24" s="5"/>
       <c r="M24" s="6"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="H25" s="5"/>
       <c r="M25" s="6"/>
     </row>
     <row r="26" spans="1:13">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="H26" s="5"/>
       <c r="M26" s="6"/>
     </row>
     <row r="27" spans="1:13">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="H27" s="5"/>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="H28" s="5"/>
       <c r="M28" s="6"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="A29" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
       <c r="D29" s="4"/>
       <c r="H29" s="5"/>
       <c r="M29" s="6"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
       <c r="D30" s="4"/>
       <c r="H30" s="5"/>
       <c r="M30" s="6"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
+      <c r="A31" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
       <c r="D31" s="4"/>
       <c r="H31" s="5"/>
       <c r="M31" s="6"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
       <c r="D32" s="4"/>
       <c r="H32" s="5"/>
       <c r="M32" s="6"/>
     </row>
     <row r="33" spans="1:13">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
       <c r="D33" s="4"/>
       <c r="H33" s="5"/>
       <c r="M33" s="6"/>
     </row>
     <row r="34" spans="1:13">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="13"/>
+      <c r="A34" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="D34" s="4"/>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
+      <c r="A35" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
       <c r="D35" s="4"/>
       <c r="H35" s="5"/>
       <c r="M35" s="6"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
+      <c r="A36" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
       <c r="D36" s="4"/>
       <c r="H36" s="5"/>
       <c r="M36" s="6"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="13"/>
+      <c r="A37" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>15</v>
+      </c>
       <c r="D37" s="4"/>
       <c r="M37" s="6"/>
     </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
+    <row r="38" spans="1:13" ht="20">
+      <c r="A38" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
       <c r="D38" s="4"/>
       <c r="H38" s="5"/>
       <c r="M38" s="6"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
+      <c r="A39" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
       <c r="D39" s="4"/>
       <c r="H39" s="5"/>
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="H40" s="5"/>
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
+      <c r="A41" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="H41" s="5"/>
       <c r="M41" s="6"/>
     </row>
     <row r="42" spans="1:13">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
+      <c r="A42" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
       <c r="D42" s="4"/>
       <c r="H42" s="5"/>
       <c r="M42" s="6"/>
     </row>
     <row r="43" spans="1:13">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
       <c r="D43" s="4"/>
       <c r="H43" s="5"/>
       <c r="M43" s="6"/>
     </row>
     <row r="44" spans="1:13">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
+      <c r="A44" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
       <c r="D44" s="4"/>
       <c r="H44" s="5"/>
       <c r="M44" s="6"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
+      <c r="A45" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
       <c r="D45" s="4"/>
       <c r="H45" s="5"/>
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
+      <c r="A46" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
       <c r="D46" s="4"/>
       <c r="H46" s="5"/>
       <c r="M46" s="6"/>
     </row>
     <row r="47" spans="1:13">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
+      <c r="A47" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D47" s="11"/>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
+      <c r="A48" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D48" s="11"/>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
     <row r="49" spans="1:13">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
+      <c r="A49" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D49" s="11"/>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
     <row r="50" spans="1:13">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
+      <c r="A50" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D50" s="11"/>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
     <row r="51" spans="1:13">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
+      <c r="A51" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D51" s="11"/>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
+      <c r="A52" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D52" s="11"/>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
     <row r="53" spans="1:13">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
+      <c r="A53" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D53" s="11"/>
       <c r="H53" s="5"/>
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
+      <c r="A54" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="D54" s="11"/>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
+      <c r="A55" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D55" s="11"/>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
+      <c r="A56" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D56" s="11"/>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
+      <c r="A57" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D57" s="11"/>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
+      <c r="A58" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D58" s="11"/>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
+      <c r="A59" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D59" s="11"/>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
+      <c r="A60" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D60" s="11"/>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
+      <c r="A61" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D61" s="11"/>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
+      <c r="A62" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D62" s="11"/>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
+      <c r="A63" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D63" s="11"/>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
+      <c r="A64" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D64" s="11"/>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
+      <c r="A65" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D65" s="11"/>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
+      <c r="A66" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D66" s="11"/>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
+      <c r="A67" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D67" s="11"/>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
+      <c r="A68" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D68" s="11"/>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
+      <c r="A69" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D69" s="11"/>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
+      <c r="A70" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D70" s="11"/>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
+      <c r="A71" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D71" s="11"/>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
+      <c r="A72" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D72" s="11"/>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
+      <c r="A73" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D73" s="11"/>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
+      <c r="A74" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D74" s="11"/>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
+      <c r="A75" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D75" s="11"/>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
+      <c r="A76" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D76" s="11"/>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
+      <c r="A77" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D77" s="11"/>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
+      <c r="A78" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D78" s="11"/>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
+      <c r="A79" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D79" s="11"/>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
+      <c r="A80" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D80" s="11"/>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
-      <c r="B81" s="2"/>
+      <c r="A81" t="s">
+        <v>171</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" t="s">
+        <v>121</v>
+      </c>
       <c r="D81" s="4"/>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
-      <c r="A82" s="11"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
+      <c r="A82" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D82" s="11"/>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
+      <c r="A83" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D83" s="11"/>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
-      <c r="A84" s="11"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
+      <c r="A84" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D84" s="11"/>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
+      <c r="A85" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D85" s="11"/>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
-      <c r="A86" s="11"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
+      <c r="A86" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D86" s="11"/>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
+      <c r="A87" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D87" s="11"/>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
+      <c r="A88" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D88" s="11"/>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
+      <c r="A89" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D89" s="11"/>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
-      <c r="A90" s="11"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
+      <c r="A90" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D90" s="11"/>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
+      <c r="A91" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D91" s="11"/>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
-      <c r="A92" s="11"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
+      <c r="A92" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D92" s="11"/>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
+      <c r="A93" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D93" s="11"/>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
-      <c r="A94" s="11"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
+      <c r="A94" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D94" s="11"/>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
+      <c r="A95" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D95" s="11"/>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
+      <c r="A96" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D96" s="11"/>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
+      <c r="A97" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D97" s="11"/>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
+      <c r="A98" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D98" s="11"/>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
+      <c r="A99" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D99" s="11"/>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
+      <c r="A100" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D100" s="11"/>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
+      <c r="A101" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D101" s="11"/>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
-      <c r="A102" s="11"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
+      <c r="A102" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D102" s="11"/>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
+      <c r="A103" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D103" s="11"/>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
+      <c r="A104" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D104" s="11"/>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
+      <c r="A105" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D105" s="11"/>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
+      <c r="A106" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D106" s="11"/>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
+      <c r="A107" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D107" s="11"/>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
+      <c r="A108" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D108" s="11"/>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
-      <c r="A109" s="11"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
+      <c r="A109" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C109" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D109" s="11"/>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
-      <c r="A110" s="11"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
+      <c r="A110" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D110" s="11"/>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
-      <c r="A111" s="11"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
+      <c r="A111" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D111" s="11"/>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
-      <c r="A112" s="11"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
+      <c r="A112" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D112" s="11"/>
       <c r="M112" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48260B21-7625-C34B-A53D-342041894CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7BFE31-9A35-4A45-AB22-5CF7321CD00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2098,6 +2098,9 @@
         <v>121</v>
       </c>
       <c r="D55" s="11"/>
+      <c r="G55">
+        <v>0.45</v>
+      </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
@@ -2111,6 +2114,9 @@
         <v>121</v>
       </c>
       <c r="D56" s="11"/>
+      <c r="G56">
+        <v>0.69</v>
+      </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
@@ -2124,6 +2130,9 @@
         <v>121</v>
       </c>
       <c r="D57" s="11"/>
+      <c r="G57">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
@@ -2137,6 +2146,9 @@
         <v>121</v>
       </c>
       <c r="D58" s="11"/>
+      <c r="G58">
+        <v>0</v>
+      </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
@@ -2150,6 +2162,9 @@
         <v>121</v>
       </c>
       <c r="D59" s="11"/>
+      <c r="G59">
+        <v>0.47</v>
+      </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
@@ -2163,6 +2178,9 @@
         <v>121</v>
       </c>
       <c r="D60" s="11"/>
+      <c r="G60">
+        <v>0.45</v>
+      </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
@@ -2176,6 +2194,9 @@
         <v>121</v>
       </c>
       <c r="D61" s="11"/>
+      <c r="G61">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
@@ -2189,6 +2210,9 @@
         <v>121</v>
       </c>
       <c r="D62" s="11"/>
+      <c r="G62">
+        <v>0</v>
+      </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
@@ -2202,6 +2226,9 @@
         <v>121</v>
       </c>
       <c r="D63" s="11"/>
+      <c r="G63">
+        <v>0.6</v>
+      </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
@@ -2215,6 +2242,9 @@
         <v>121</v>
       </c>
       <c r="D64" s="11"/>
+      <c r="G64">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
@@ -2228,6 +2258,9 @@
         <v>121</v>
       </c>
       <c r="D65" s="11"/>
+      <c r="G65">
+        <v>0</v>
+      </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
@@ -2241,6 +2274,9 @@
         <v>121</v>
       </c>
       <c r="D66" s="11"/>
+      <c r="G66">
+        <v>0.27</v>
+      </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
@@ -2254,6 +2290,9 @@
         <v>121</v>
       </c>
       <c r="D67" s="11"/>
+      <c r="G67">
+        <v>0.45</v>
+      </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
@@ -2267,6 +2306,9 @@
         <v>121</v>
       </c>
       <c r="D68" s="11"/>
+      <c r="G68">
+        <v>0.6</v>
+      </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
@@ -2280,6 +2322,9 @@
         <v>121</v>
       </c>
       <c r="D69" s="11"/>
+      <c r="G69">
+        <v>0.42</v>
+      </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
@@ -2293,6 +2338,9 @@
         <v>121</v>
       </c>
       <c r="D70" s="11"/>
+      <c r="G70">
+        <v>0.4</v>
+      </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
@@ -2306,6 +2354,9 @@
         <v>121</v>
       </c>
       <c r="D71" s="11"/>
+      <c r="G71">
+        <v>0.4</v>
+      </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
@@ -2319,6 +2370,9 @@
         <v>121</v>
       </c>
       <c r="D72" s="11"/>
+      <c r="G72">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
@@ -2332,6 +2386,9 @@
         <v>121</v>
       </c>
       <c r="D73" s="11"/>
+      <c r="G73">
+        <v>0.06</v>
+      </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
@@ -2345,6 +2402,9 @@
         <v>121</v>
       </c>
       <c r="D74" s="11"/>
+      <c r="G74">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
@@ -2358,6 +2418,9 @@
         <v>121</v>
       </c>
       <c r="D75" s="11"/>
+      <c r="G75">
+        <v>0.5</v>
+      </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
@@ -2371,6 +2434,9 @@
         <v>121</v>
       </c>
       <c r="D76" s="11"/>
+      <c r="G76">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
@@ -2384,6 +2450,9 @@
         <v>121</v>
       </c>
       <c r="D77" s="11"/>
+      <c r="G77">
+        <v>0.59</v>
+      </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
@@ -2397,6 +2466,9 @@
         <v>121</v>
       </c>
       <c r="D78" s="11"/>
+      <c r="G78">
+        <v>0.08</v>
+      </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
@@ -2410,6 +2482,9 @@
         <v>121</v>
       </c>
       <c r="D79" s="11"/>
+      <c r="G79">
+        <v>0.71</v>
+      </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
@@ -2423,6 +2498,9 @@
         <v>121</v>
       </c>
       <c r="D80" s="11"/>
+      <c r="G80">
+        <v>0.46</v>
+      </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
@@ -2436,6 +2514,9 @@
         <v>121</v>
       </c>
       <c r="D81" s="4"/>
+      <c r="G81">
+        <v>0.4</v>
+      </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
@@ -2449,6 +2530,9 @@
         <v>121</v>
       </c>
       <c r="D82" s="11"/>
+      <c r="G82">
+        <v>0.15</v>
+      </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
@@ -2462,6 +2546,9 @@
         <v>121</v>
       </c>
       <c r="D83" s="11"/>
+      <c r="G83">
+        <v>0.37</v>
+      </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
@@ -2475,6 +2562,9 @@
         <v>121</v>
       </c>
       <c r="D84" s="11"/>
+      <c r="G84">
+        <v>0.59</v>
+      </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
@@ -2488,6 +2578,9 @@
         <v>121</v>
       </c>
       <c r="D85" s="11"/>
+      <c r="G85">
+        <v>0.59</v>
+      </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
@@ -2501,6 +2594,9 @@
         <v>121</v>
       </c>
       <c r="D86" s="11"/>
+      <c r="G86">
+        <v>0.65</v>
+      </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
@@ -2514,6 +2610,9 @@
         <v>121</v>
       </c>
       <c r="D87" s="11"/>
+      <c r="G87">
+        <v>0.65</v>
+      </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
@@ -2527,6 +2626,9 @@
         <v>121</v>
       </c>
       <c r="D88" s="11"/>
+      <c r="G88">
+        <v>0.54</v>
+      </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
@@ -2540,6 +2642,9 @@
         <v>121</v>
       </c>
       <c r="D89" s="11"/>
+      <c r="G89">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
@@ -2553,6 +2658,9 @@
         <v>121</v>
       </c>
       <c r="D90" s="11"/>
+      <c r="G90">
+        <v>0.44</v>
+      </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
@@ -2566,6 +2674,9 @@
         <v>121</v>
       </c>
       <c r="D91" s="11"/>
+      <c r="G91">
+        <v>0.53</v>
+      </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
@@ -2579,6 +2690,9 @@
         <v>121</v>
       </c>
       <c r="D92" s="11"/>
+      <c r="G92">
+        <v>0.71</v>
+      </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
@@ -2592,6 +2706,9 @@
         <v>121</v>
       </c>
       <c r="D93" s="11"/>
+      <c r="G93">
+        <v>0.63</v>
+      </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
@@ -2605,6 +2722,9 @@
         <v>121</v>
       </c>
       <c r="D94" s="11"/>
+      <c r="G94">
+        <v>0</v>
+      </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
@@ -2618,6 +2738,9 @@
         <v>121</v>
       </c>
       <c r="D95" s="11"/>
+      <c r="G95">
+        <v>0.51</v>
+      </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
@@ -2631,6 +2754,9 @@
         <v>121</v>
       </c>
       <c r="D96" s="11"/>
+      <c r="G96">
+        <v>0</v>
+      </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
@@ -2644,6 +2770,9 @@
         <v>121</v>
       </c>
       <c r="D97" s="11"/>
+      <c r="G97">
+        <v>0.62</v>
+      </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
@@ -2657,6 +2786,9 @@
         <v>121</v>
       </c>
       <c r="D98" s="11"/>
+      <c r="G98">
+        <v>0.54</v>
+      </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
@@ -2670,6 +2802,9 @@
         <v>121</v>
       </c>
       <c r="D99" s="11"/>
+      <c r="G99">
+        <v>0</v>
+      </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
@@ -2683,6 +2818,9 @@
         <v>121</v>
       </c>
       <c r="D100" s="11"/>
+      <c r="G100">
+        <v>0.72</v>
+      </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
@@ -2696,6 +2834,9 @@
         <v>121</v>
       </c>
       <c r="D101" s="11"/>
+      <c r="G101">
+        <v>0.33</v>
+      </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
@@ -2709,6 +2850,9 @@
         <v>121</v>
       </c>
       <c r="D102" s="11"/>
+      <c r="G102">
+        <v>0.32</v>
+      </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
@@ -2722,6 +2866,9 @@
         <v>121</v>
       </c>
       <c r="D103" s="11"/>
+      <c r="G103">
+        <v>0.44</v>
+      </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
@@ -2735,6 +2882,9 @@
         <v>121</v>
       </c>
       <c r="D104" s="11"/>
+      <c r="G104">
+        <v>0.59</v>
+      </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
@@ -2748,6 +2898,9 @@
         <v>121</v>
       </c>
       <c r="D105" s="11"/>
+      <c r="G105">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
@@ -2761,6 +2914,9 @@
         <v>121</v>
       </c>
       <c r="D106" s="11"/>
+      <c r="G106">
+        <v>0.47</v>
+      </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
@@ -2774,6 +2930,9 @@
         <v>121</v>
       </c>
       <c r="D107" s="11"/>
+      <c r="G107">
+        <v>0.54</v>
+      </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
@@ -2787,6 +2946,9 @@
         <v>121</v>
       </c>
       <c r="D108" s="11"/>
+      <c r="G108">
+        <v>0.63</v>
+      </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
@@ -2800,6 +2962,9 @@
         <v>121</v>
       </c>
       <c r="D109" s="11"/>
+      <c r="G109">
+        <v>0.53</v>
+      </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
@@ -2813,6 +2978,9 @@
         <v>121</v>
       </c>
       <c r="D110" s="11"/>
+      <c r="G110">
+        <v>0.49</v>
+      </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
@@ -2826,6 +2994,9 @@
         <v>121</v>
       </c>
       <c r="D111" s="11"/>
+      <c r="G111">
+        <v>0.54</v>
+      </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
@@ -2839,6 +3010,9 @@
         <v>121</v>
       </c>
       <c r="D112" s="11"/>
+      <c r="G112">
+        <v>0.51</v>
+      </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7BFE31-9A35-4A45-AB22-5CF7321CD00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F47528C-A00B-C14B-8920-99D349365C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="D79" s="11"/>
       <c r="G79">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="M79" s="6"/>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="D99" s="11"/>
       <c r="G99">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="M99" s="6"/>
     </row>

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F47528C-A00B-C14B-8920-99D349365C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66253EB0-95DD-C040-B79D-FA08A9B3AE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1359,6 +1359,9 @@
         <v>15</v>
       </c>
       <c r="D2" s="4"/>
+      <c r="G2">
+        <v>0.32</v>
+      </c>
       <c r="H2" s="5"/>
       <c r="M2" s="18"/>
     </row>
@@ -1373,6 +1376,9 @@
         <v>15</v>
       </c>
       <c r="D3" s="4"/>
+      <c r="G3">
+        <v>0.64</v>
+      </c>
       <c r="H3" s="5"/>
       <c r="M3" s="18"/>
     </row>
@@ -1387,6 +1393,9 @@
         <v>15</v>
       </c>
       <c r="D4" s="4"/>
+      <c r="G4">
+        <v>0.41</v>
+      </c>
       <c r="H4" s="5"/>
       <c r="M4" s="18"/>
     </row>
@@ -1401,6 +1410,9 @@
         <v>15</v>
       </c>
       <c r="D5" s="4"/>
+      <c r="G5">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="M5" s="18"/>
     </row>
@@ -1415,6 +1427,9 @@
         <v>15</v>
       </c>
       <c r="D6" s="4"/>
+      <c r="G6">
+        <v>0.59</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="M6" s="6"/>
     </row>
@@ -1429,6 +1444,9 @@
         <v>15</v>
       </c>
       <c r="D7" s="4"/>
+      <c r="G7">
+        <v>0.34</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="M7" s="6"/>
     </row>
@@ -1443,6 +1461,9 @@
         <v>15</v>
       </c>
       <c r="D8" s="4"/>
+      <c r="G8">
+        <v>0.3</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="M8" s="6"/>
     </row>
@@ -1457,6 +1478,9 @@
         <v>15</v>
       </c>
       <c r="D9" s="4"/>
+      <c r="G9">
+        <v>0.43</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="M9" s="6"/>
     </row>
@@ -1471,6 +1495,9 @@
         <v>15</v>
       </c>
       <c r="D10" s="4"/>
+      <c r="G10">
+        <v>0.48</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="M10" s="6"/>
     </row>
@@ -1485,6 +1512,9 @@
         <v>15</v>
       </c>
       <c r="D11" s="4"/>
+      <c r="G11">
+        <v>0.73</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="M11" s="6"/>
     </row>
@@ -1499,6 +1529,9 @@
         <v>15</v>
       </c>
       <c r="D12" s="4"/>
+      <c r="G12">
+        <v>0.45</v>
+      </c>
       <c r="H12" s="5"/>
       <c r="M12" s="6"/>
     </row>
@@ -1513,6 +1546,9 @@
         <v>15</v>
       </c>
       <c r="D13" s="4"/>
+      <c r="G13">
+        <v>0.59</v>
+      </c>
       <c r="H13" s="5"/>
       <c r="M13" s="6"/>
     </row>
@@ -1527,6 +1563,9 @@
         <v>15</v>
       </c>
       <c r="D14" s="4"/>
+      <c r="G14">
+        <v>0.27</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="M14" s="6"/>
     </row>
@@ -1541,6 +1580,9 @@
         <v>15</v>
       </c>
       <c r="D15" s="4"/>
+      <c r="G15">
+        <v>0.2</v>
+      </c>
       <c r="H15" s="5"/>
       <c r="M15" s="6"/>
     </row>
@@ -1555,6 +1597,9 @@
         <v>15</v>
       </c>
       <c r="D16" s="4"/>
+      <c r="G16">
+        <v>0.36</v>
+      </c>
       <c r="H16" s="5"/>
       <c r="M16" s="6"/>
     </row>
@@ -1569,6 +1614,9 @@
         <v>15</v>
       </c>
       <c r="D17" s="4"/>
+      <c r="G17">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="H17" s="5"/>
       <c r="M17" s="6"/>
     </row>
@@ -1583,6 +1631,9 @@
         <v>15</v>
       </c>
       <c r="D18" s="4"/>
+      <c r="G18">
+        <v>0.41</v>
+      </c>
       <c r="H18" s="5"/>
       <c r="M18" s="6"/>
     </row>
@@ -1597,6 +1648,9 @@
         <v>15</v>
       </c>
       <c r="D19" s="4"/>
+      <c r="G19">
+        <v>0.32</v>
+      </c>
       <c r="H19" s="5"/>
       <c r="M19" s="6"/>
     </row>
@@ -1611,6 +1665,9 @@
         <v>15</v>
       </c>
       <c r="D20" s="4"/>
+      <c r="G20">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="H20" s="5"/>
       <c r="M20" s="6"/>
     </row>
@@ -1625,6 +1682,9 @@
         <v>15</v>
       </c>
       <c r="D21" s="4"/>
+      <c r="G21">
+        <v>0.61</v>
+      </c>
       <c r="H21" s="5"/>
       <c r="M21" s="6"/>
     </row>
@@ -1639,6 +1699,9 @@
         <v>15</v>
       </c>
       <c r="D22" s="4"/>
+      <c r="G22">
+        <v>0.39</v>
+      </c>
       <c r="H22" s="5"/>
       <c r="M22" s="6"/>
     </row>
@@ -1653,6 +1716,9 @@
         <v>15</v>
       </c>
       <c r="D23" s="4"/>
+      <c r="G23">
+        <v>0.23</v>
+      </c>
       <c r="H23" s="5"/>
       <c r="M23" s="6"/>
     </row>
@@ -1667,6 +1733,9 @@
         <v>15</v>
       </c>
       <c r="D24" s="4"/>
+      <c r="G24">
+        <v>0.45</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="M24" s="6"/>
     </row>
@@ -1681,6 +1750,9 @@
         <v>15</v>
       </c>
       <c r="D25" s="4"/>
+      <c r="G25">
+        <v>0.41</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="M25" s="6"/>
     </row>
@@ -1695,6 +1767,9 @@
         <v>15</v>
       </c>
       <c r="D26" s="4"/>
+      <c r="G26">
+        <v>0.3</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="M26" s="6"/>
     </row>
@@ -1709,6 +1784,9 @@
         <v>15</v>
       </c>
       <c r="D27" s="4"/>
+      <c r="G27">
+        <v>0.3</v>
+      </c>
       <c r="H27" s="5"/>
       <c r="M27" s="6"/>
     </row>
@@ -1723,6 +1801,9 @@
         <v>15</v>
       </c>
       <c r="D28" s="4"/>
+      <c r="G28">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="H28" s="5"/>
       <c r="M28" s="6"/>
     </row>
@@ -1737,6 +1818,9 @@
         <v>15</v>
       </c>
       <c r="D29" s="4"/>
+      <c r="G29">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="H29" s="5"/>
       <c r="M29" s="6"/>
     </row>
@@ -1751,6 +1835,9 @@
         <v>15</v>
       </c>
       <c r="D30" s="4"/>
+      <c r="G30">
+        <v>0.5</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="M30" s="6"/>
     </row>
@@ -1765,6 +1852,9 @@
         <v>15</v>
       </c>
       <c r="D31" s="4"/>
+      <c r="G31">
+        <v>0.32</v>
+      </c>
       <c r="H31" s="5"/>
       <c r="M31" s="6"/>
     </row>
@@ -1779,6 +1869,9 @@
         <v>15</v>
       </c>
       <c r="D32" s="4"/>
+      <c r="G32">
+        <v>0.36</v>
+      </c>
       <c r="H32" s="5"/>
       <c r="M32" s="6"/>
     </row>
@@ -1793,6 +1886,9 @@
         <v>15</v>
       </c>
       <c r="D33" s="4"/>
+      <c r="G33">
+        <v>0.23</v>
+      </c>
       <c r="H33" s="5"/>
       <c r="M33" s="6"/>
     </row>
@@ -1807,6 +1903,9 @@
         <v>15</v>
       </c>
       <c r="D34" s="4"/>
+      <c r="G34">
+        <v>0.52</v>
+      </c>
       <c r="M34" s="6"/>
     </row>
     <row r="35" spans="1:13">
@@ -1820,6 +1919,9 @@
         <v>15</v>
       </c>
       <c r="D35" s="4"/>
+      <c r="G35">
+        <v>0</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="M35" s="6"/>
     </row>
@@ -1834,6 +1936,9 @@
         <v>15</v>
       </c>
       <c r="D36" s="4"/>
+      <c r="G36">
+        <v>0.39</v>
+      </c>
       <c r="H36" s="5"/>
       <c r="M36" s="6"/>
     </row>
@@ -1848,6 +1953,9 @@
         <v>15</v>
       </c>
       <c r="D37" s="4"/>
+      <c r="G37">
+        <v>0.45</v>
+      </c>
       <c r="M37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20">
@@ -1861,6 +1969,9 @@
         <v>15</v>
       </c>
       <c r="D38" s="4"/>
+      <c r="G38">
+        <v>0.34</v>
+      </c>
       <c r="H38" s="5"/>
       <c r="M38" s="6"/>
     </row>
@@ -1875,6 +1986,9 @@
         <v>15</v>
       </c>
       <c r="D39" s="4"/>
+      <c r="G39">
+        <v>0.77</v>
+      </c>
       <c r="H39" s="5"/>
       <c r="M39" s="6"/>
     </row>
@@ -1889,6 +2003,9 @@
         <v>15</v>
       </c>
       <c r="D40" s="4"/>
+      <c r="G40">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="H40" s="5"/>
       <c r="M40" s="6"/>
     </row>
@@ -1903,6 +2020,9 @@
         <v>15</v>
       </c>
       <c r="D41" s="4"/>
+      <c r="G41">
+        <v>0.59</v>
+      </c>
       <c r="H41" s="5"/>
       <c r="M41" s="6"/>
     </row>
@@ -1917,6 +2037,9 @@
         <v>15</v>
       </c>
       <c r="D42" s="4"/>
+      <c r="G42">
+        <v>0.52</v>
+      </c>
       <c r="H42" s="5"/>
       <c r="M42" s="6"/>
     </row>
@@ -1931,6 +2054,9 @@
         <v>15</v>
       </c>
       <c r="D43" s="4"/>
+      <c r="G43">
+        <v>0.56999999999999995</v>
+      </c>
       <c r="H43" s="5"/>
       <c r="M43" s="6"/>
     </row>
@@ -1945,6 +2071,9 @@
         <v>15</v>
       </c>
       <c r="D44" s="4"/>
+      <c r="G44">
+        <v>0.36</v>
+      </c>
       <c r="H44" s="5"/>
       <c r="M44" s="6"/>
     </row>
@@ -1959,6 +2088,9 @@
         <v>15</v>
       </c>
       <c r="D45" s="4"/>
+      <c r="G45">
+        <v>0.68</v>
+      </c>
       <c r="H45" s="5"/>
       <c r="M45" s="6"/>
     </row>
@@ -1973,6 +2105,9 @@
         <v>15</v>
       </c>
       <c r="D46" s="4"/>
+      <c r="G46">
+        <v>0.5</v>
+      </c>
       <c r="H46" s="5"/>
       <c r="M46" s="6"/>
     </row>
@@ -1987,6 +2122,9 @@
         <v>15</v>
       </c>
       <c r="D47" s="11"/>
+      <c r="G47">
+        <v>0.52</v>
+      </c>
       <c r="H47" s="5"/>
       <c r="M47" s="6"/>
     </row>
@@ -2001,6 +2139,9 @@
         <v>15</v>
       </c>
       <c r="D48" s="11"/>
+      <c r="G48">
+        <v>0.52</v>
+      </c>
       <c r="H48" s="5"/>
       <c r="M48" s="6"/>
     </row>
@@ -2015,6 +2156,9 @@
         <v>15</v>
       </c>
       <c r="D49" s="11"/>
+      <c r="G49">
+        <v>0.39</v>
+      </c>
       <c r="H49" s="5"/>
       <c r="M49" s="6"/>
     </row>
@@ -2029,6 +2173,9 @@
         <v>15</v>
       </c>
       <c r="D50" s="11"/>
+      <c r="G50">
+        <v>0.23</v>
+      </c>
       <c r="H50" s="5"/>
       <c r="M50" s="6"/>
     </row>
@@ -2043,6 +2190,9 @@
         <v>15</v>
       </c>
       <c r="D51" s="11"/>
+      <c r="G51">
+        <v>0.66</v>
+      </c>
       <c r="H51" s="5"/>
       <c r="M51" s="6"/>
     </row>
@@ -2057,6 +2207,9 @@
         <v>15</v>
       </c>
       <c r="D52" s="11"/>
+      <c r="G52">
+        <v>0.45</v>
+      </c>
       <c r="H52" s="5"/>
       <c r="M52" s="6"/>
     </row>
@@ -2071,6 +2224,9 @@
         <v>15</v>
       </c>
       <c r="D53" s="11"/>
+      <c r="G53">
+        <v>0.34</v>
+      </c>
       <c r="H53" s="5"/>
       <c r="M53" s="6"/>
     </row>
@@ -2085,6 +2241,9 @@
         <v>15</v>
       </c>
       <c r="D54" s="11"/>
+      <c r="G54">
+        <v>0.5</v>
+      </c>
       <c r="M54" s="6"/>
     </row>
     <row r="55" spans="1:13">

--- a/cw21062026.xlsx
+++ b/cw21062026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66253EB0-95DD-C040-B79D-FA08A9B3AE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2095E53-1B42-6447-ACE4-E43E46711CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="234">
   <si>
     <t>Surname</t>
   </si>
@@ -2260,6 +2260,9 @@
       <c r="G55">
         <v>0.45</v>
       </c>
+      <c r="H55" s="4">
+        <v>0.48</v>
+      </c>
       <c r="M55" s="6"/>
     </row>
     <row r="56" spans="1:13">
@@ -2276,6 +2279,9 @@
       <c r="G56">
         <v>0.69</v>
       </c>
+      <c r="H56" s="4">
+        <v>0.65</v>
+      </c>
       <c r="M56" s="6"/>
     </row>
     <row r="57" spans="1:13">
@@ -2292,6 +2298,9 @@
       <c r="G57">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H57" s="4">
+        <v>0.54</v>
+      </c>
       <c r="M57" s="6"/>
     </row>
     <row r="58" spans="1:13">
@@ -2308,6 +2317,9 @@
       <c r="G58">
         <v>0</v>
       </c>
+      <c r="H58" s="4">
+        <v>0.46</v>
+      </c>
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13">
@@ -2324,6 +2336,9 @@
       <c r="G59">
         <v>0.47</v>
       </c>
+      <c r="H59" s="4">
+        <v>0.65</v>
+      </c>
       <c r="M59" s="6"/>
     </row>
     <row r="60" spans="1:13">
@@ -2340,6 +2355,9 @@
       <c r="G60">
         <v>0.45</v>
       </c>
+      <c r="H60" s="4">
+        <v>0</v>
+      </c>
       <c r="M60" s="6"/>
     </row>
     <row r="61" spans="1:13">
@@ -2356,6 +2374,9 @@
       <c r="G61">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H61" s="4">
+        <v>0.31</v>
+      </c>
       <c r="M61" s="6"/>
     </row>
     <row r="62" spans="1:13">
@@ -2372,6 +2393,9 @@
       <c r="G62">
         <v>0</v>
       </c>
+      <c r="H62" s="4">
+        <v>0</v>
+      </c>
       <c r="M62" s="6"/>
     </row>
     <row r="63" spans="1:13">
@@ -2388,6 +2412,9 @@
       <c r="G63">
         <v>0.6</v>
       </c>
+      <c r="H63" s="4">
+        <v>0.71</v>
+      </c>
       <c r="M63" s="6"/>
     </row>
     <row r="64" spans="1:13">
@@ -2404,6 +2431,9 @@
       <c r="G64">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H64" s="4">
+        <v>0.54</v>
+      </c>
       <c r="M64" s="6"/>
     </row>
     <row r="65" spans="1:13">
@@ -2420,6 +2450,9 @@
       <c r="G65">
         <v>0</v>
       </c>
+      <c r="H65" s="4">
+        <v>0</v>
+      </c>
       <c r="M65" s="6"/>
     </row>
     <row r="66" spans="1:13">
@@ -2436,6 +2469,9 @@
       <c r="G66">
         <v>0.27</v>
       </c>
+      <c r="H66" s="4">
+        <v>0.63</v>
+      </c>
       <c r="M66" s="6"/>
     </row>
     <row r="67" spans="1:13">
@@ -2452,6 +2488,9 @@
       <c r="G67">
         <v>0.45</v>
       </c>
+      <c r="H67" s="4">
+        <v>0</v>
+      </c>
       <c r="M67" s="6"/>
     </row>
     <row r="68" spans="1:13">
@@ -2468,6 +2507,9 @@
       <c r="G68">
         <v>0.6</v>
       </c>
+      <c r="H68" s="4">
+        <v>0.33</v>
+      </c>
       <c r="M68" s="6"/>
     </row>
     <row r="69" spans="1:13">
@@ -2484,6 +2526,9 @@
       <c r="G69">
         <v>0.42</v>
       </c>
+      <c r="H69" s="4">
+        <v>0.63</v>
+      </c>
       <c r="M69" s="6"/>
     </row>
     <row r="70" spans="1:13">
@@ -2500,6 +2545,9 @@
       <c r="G70">
         <v>0.4</v>
       </c>
+      <c r="H70" s="4">
+        <v>0.31</v>
+      </c>
       <c r="M70" s="6"/>
     </row>
     <row r="71" spans="1:13">
@@ -2516,6 +2564,9 @@
       <c r="G71">
         <v>0.4</v>
       </c>
+      <c r="H71" s="4">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M71" s="6"/>
     </row>
     <row r="72" spans="1:13">
@@ -2532,6 +2583,9 @@
       <c r="G72">
         <v>0.28000000000000003</v>
       </c>
+      <c r="H72" s="4">
+        <v>0.31</v>
+      </c>
       <c r="M72" s="6"/>
     </row>
     <row r="73" spans="1:13">
@@ -2548,6 +2602,9 @@
       <c r="G73">
         <v>0.06</v>
       </c>
+      <c r="H73" s="4">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="M73" s="6"/>
     </row>
     <row r="74" spans="1:13">
@@ -2564,6 +2621,9 @@
       <c r="G74">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H74" s="4">
+        <v>0.38</v>
+      </c>
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13">
@@ -2580,6 +2640,9 @@
       <c r="G75">
         <v>0.5</v>
       </c>
+      <c r="H75" s="4">
+        <v>0</v>
+      </c>
       <c r="M75" s="6"/>
     </row>
     <row r="76" spans="1:13">
@@ -2596,6 +2659,9 @@
       <c r="G76">
         <v>0.28999999999999998</v>
       </c>
+      <c r="H76" s="4">
+        <v>0.31</v>
+      </c>
       <c r="M76" s="6"/>
     </row>
     <row r="77" spans="1:13">
@@ -2612,6 +2678,9 @@
       <c r="G77">
         <v>0.59</v>
       </c>
+      <c r="H77" s="4">
+        <v>0.88</v>
+      </c>
       <c r="M77" s="6"/>
     </row>
     <row r="78" spans="1:13">
@@ -2628,6 +2697,9 @@
       <c r="G78">
         <v>0.08</v>
       </c>
+      <c r="H78" s="4">
+        <v>0.27</v>
+      </c>
       <c r="M78" s="6"/>
     </row>
     <row r="79" spans="1:13">
@@ -2644,6 +2716,9 @@
       <c r="G79">
         <v>0.72</v>
       </c>
+      <c r="H79" s="4">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="M79" s="6"/>
     </row>
     <row r="80" spans="1:13">
@@ -2660,6 +2735,9 @@
       <c r="G80">
         <v>0.46</v>
       </c>
+      <c r="H80" s="4">
+        <v>0.6</v>
+      </c>
       <c r="M80" s="6"/>
     </row>
     <row r="81" spans="1:13">
@@ -2676,6 +2754,9 @@
       <c r="G81">
         <v>0.4</v>
       </c>
+      <c r="H81" s="4">
+        <v>0.31</v>
+      </c>
       <c r="M81" s="6"/>
     </row>
     <row r="82" spans="1:13">
@@ -2692,6 +2773,9 @@
       <c r="G82">
         <v>0.15</v>
       </c>
+      <c r="H82" s="4">
+        <v>0.35</v>
+      </c>
       <c r="M82" s="6"/>
     </row>
     <row r="83" spans="1:13">
@@ -2708,6 +2792,9 @@
       <c r="G83">
         <v>0.37</v>
       </c>
+      <c r="H83" s="4">
+        <v>0.38</v>
+      </c>
       <c r="M83" s="6"/>
     </row>
     <row r="84" spans="1:13">
@@ -2724,6 +2811,9 @@
       <c r="G84">
         <v>0.59</v>
       </c>
+      <c r="H84" s="4">
+        <v>0.46</v>
+      </c>
       <c r="M84" s="6"/>
     </row>
     <row r="85" spans="1:13">
@@ -2740,6 +2830,9 @@
       <c r="G85">
         <v>0.59</v>
       </c>
+      <c r="H85" s="4">
+        <v>0.44</v>
+      </c>
       <c r="M85" s="6"/>
     </row>
     <row r="86" spans="1:13">
@@ -2756,6 +2849,9 @@
       <c r="G86">
         <v>0.65</v>
       </c>
+      <c r="H86" s="4">
+        <v>0.52</v>
+      </c>
       <c r="M86" s="6"/>
     </row>
     <row r="87" spans="1:13">
@@ -2772,6 +2868,9 @@
       <c r="G87">
         <v>0.65</v>
       </c>
+      <c r="H87" s="4">
+        <v>0.83</v>
+      </c>
       <c r="M87" s="6"/>
     </row>
     <row r="88" spans="1:13">
@@ -2788,6 +2887,9 @@
       <c r="G88">
         <v>0.54</v>
       </c>
+      <c r="H88" s="4">
+        <v>0.67</v>
+      </c>
       <c r="M88" s="6"/>
     </row>
     <row r="89" spans="1:13">
@@ -2804,6 +2906,9 @@
       <c r="G89">
         <v>0.56000000000000005</v>
       </c>
+      <c r="H89" s="4">
+        <v>0.9</v>
+      </c>
       <c r="M89" s="6"/>
     </row>
     <row r="90" spans="1:13">
@@ -2820,6 +2925,9 @@
       <c r="G90">
         <v>0.44</v>
       </c>
+      <c r="H90" s="4">
+        <v>0.75</v>
+      </c>
       <c r="M90" s="6"/>
     </row>
     <row r="91" spans="1:13">
@@ -2836,6 +2944,9 @@
       <c r="G91">
         <v>0.53</v>
       </c>
+      <c r="H91" s="4">
+        <v>0</v>
+      </c>
       <c r="M91" s="6"/>
     </row>
     <row r="92" spans="1:13">
@@ -2852,6 +2963,9 @@
       <c r="G92">
         <v>0.71</v>
       </c>
+      <c r="H92" s="4">
+        <v>0.42</v>
+      </c>
       <c r="M92" s="6"/>
     </row>
     <row r="93" spans="1:13">
@@ -2868,6 +2982,9 @@
       <c r="G93">
         <v>0.63</v>
       </c>
+      <c r="H93" s="4">
+        <v>0.46</v>
+      </c>
       <c r="M93" s="6"/>
     </row>
     <row r="94" spans="1:13">
@@ -2884,6 +3001,9 @@
       <c r="G94">
         <v>0</v>
       </c>
+      <c r="H94" s="4">
+        <v>0</v>
+      </c>
       <c r="M94" s="6"/>
     </row>
     <row r="95" spans="1:13">
@@ -2900,6 +3020,9 @@
       <c r="G95">
         <v>0.51</v>
       </c>
+      <c r="H95" s="4">
+        <v>0.52</v>
+      </c>
       <c r="M95" s="6"/>
     </row>
     <row r="96" spans="1:13">
@@ -2916,6 +3039,9 @@
       <c r="G96">
         <v>0</v>
       </c>
+      <c r="H96" s="4">
+        <v>0</v>
+      </c>
       <c r="M96" s="6"/>
     </row>
     <row r="97" spans="1:13">
@@ -2932,6 +3058,9 @@
       <c r="G97">
         <v>0.62</v>
       </c>
+      <c r="H97" s="4">
+        <v>0.54</v>
+      </c>
       <c r="M97" s="6"/>
     </row>
     <row r="98" spans="1:13">
@@ -2948,6 +3077,9 @@
       <c r="G98">
         <v>0.54</v>
       </c>
+      <c r="H98" s="4">
+        <v>0.65</v>
+      </c>
       <c r="M98" s="6"/>
     </row>
     <row r="99" spans="1:13">
@@ -2964,6 +3096,9 @@
       <c r="G99">
         <v>0.19</v>
       </c>
+      <c r="H99" s="4">
+        <v>0.46</v>
+      </c>
       <c r="M99" s="6"/>
     </row>
     <row r="100" spans="1:13">
@@ -2980,6 +3115,9 @@
       <c r="G100">
         <v>0.72</v>
       </c>
+      <c r="H100" s="4">
+        <v>0.79</v>
+      </c>
       <c r="M100" s="6"/>
     </row>
     <row r="101" spans="1:13">
@@ -2996,6 +3134,9 @@
       <c r="G101">
         <v>0.33</v>
       </c>
+      <c r="H101" s="4">
+        <v>0.38</v>
+      </c>
       <c r="M101" s="6"/>
     </row>
     <row r="102" spans="1:13">
@@ -3012,6 +3153,9 @@
       <c r="G102">
         <v>0.32</v>
       </c>
+      <c r="H102" s="4">
+        <v>0.44</v>
+      </c>
       <c r="M102" s="6"/>
     </row>
     <row r="103" spans="1:13">
@@ -3028,6 +3172,9 @@
       <c r="G103">
         <v>0.44</v>
       </c>
+      <c r="H103" s="4">
+        <v>0</v>
+      </c>
       <c r="M103" s="6"/>
     </row>
     <row r="104" spans="1:13">
@@ -3044,6 +3191,9 @@
       <c r="G104">
         <v>0.59</v>
       </c>
+      <c r="H104" s="4">
+        <v>0.42</v>
+      </c>
       <c r="M104" s="6"/>
     </row>
     <row r="105" spans="1:13">
@@ -3060,6 +3210,9 @@
       <c r="G105">
         <v>0.57999999999999996</v>
       </c>
+      <c r="H105" s="4">
+        <v>0.71</v>
+      </c>
       <c r="M105" s="6"/>
     </row>
     <row r="106" spans="1:13">
@@ -3076,6 +3229,9 @@
       <c r="G106">
         <v>0.47</v>
       </c>
+      <c r="H106" s="4">
+        <v>0.28999999999999998</v>
+      </c>
       <c r="M106" s="6"/>
     </row>
     <row r="107" spans="1:13">
@@ -3092,6 +3248,9 @@
       <c r="G107">
         <v>0.54</v>
       </c>
+      <c r="H107" s="4">
+        <v>0.67</v>
+      </c>
       <c r="M107" s="6"/>
     </row>
     <row r="108" spans="1:13">
@@ -3108,6 +3267,9 @@
       <c r="G108">
         <v>0.63</v>
       </c>
+      <c r="H108" s="4">
+        <v>0.83</v>
+      </c>
       <c r="M108" s="6"/>
     </row>
     <row r="109" spans="1:13">
@@ -3124,6 +3286,9 @@
       <c r="G109">
         <v>0.53</v>
       </c>
+      <c r="H109" s="4">
+        <v>0.79</v>
+      </c>
       <c r="M109" s="6"/>
     </row>
     <row r="110" spans="1:13">
@@ -3140,6 +3305,9 @@
       <c r="G110">
         <v>0.49</v>
       </c>
+      <c r="H110" s="4">
+        <v>0.46</v>
+      </c>
       <c r="M110" s="6"/>
     </row>
     <row r="111" spans="1:13">
@@ -3156,6 +3324,9 @@
       <c r="G111">
         <v>0.54</v>
       </c>
+      <c r="H111" s="4">
+        <v>0.44</v>
+      </c>
       <c r="M111" s="6"/>
     </row>
     <row r="112" spans="1:13">
@@ -3172,13 +3343,24 @@
       <c r="G112">
         <v>0.51</v>
       </c>
+      <c r="H112" s="4">
+        <v>0</v>
+      </c>
       <c r="M112" s="6"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="11"/>
       <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
+      <c r="C113" s="11" t="s">
+        <v>121</v>
+      </c>
       <c r="D113" s="11"/>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113" s="4">
+        <v>0.1</v>
+      </c>
       <c r="M113" s="6"/>
     </row>
     <row r="114" spans="1:13">
